--- a/redmine-logger/timelog.xlsx
+++ b/redmine-logger/timelog.xlsx
@@ -1,34 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TimeLog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="3">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +66,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +153,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +188,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +223,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,97 +354,521 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D33"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>issue_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
+      <c r="A1" s="1" t="str">
+        <v>date</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <v>issue_id</v>
+      </c>
+      <c r="C1" s="1" t="str">
+        <v>hours</v>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v>comments</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>158484</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>UI Fix</t>
-        </is>
+      <c r="A2" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B2" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v>YTP - LA height and weight entered details  are not appearing after recalculating BI from Review Details screen and the Make Payment screen.</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>158484</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bug Fix</t>
-        </is>
+      <c r="A3" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B3" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>CM/FT logic is not working for the spouse screen</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>158484</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>API Development</t>
-        </is>
+      <c r="A4" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B4" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>In YTP height detail is showing as “NA” on the Review Details screen.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B5" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v>annur journey is completed still Proceed now is displayed on the screen to procced again for  annur</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B6" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <v>Like sone screen header content is - Employer details , e-insurance account details ---(not clear this for la or pr)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B7" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B8" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Photo Alignment Issue
+There is an alignment issue on the first page of the proposal form caused by the photo size.</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B9" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">SP Code Missing
+The SP code is not being populated in the proposal form first page.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B10" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <v>On the Review details screen header and below section not clear this is for la or pr</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B11" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <v>After recalculate -The Bank Name and Bank Branch Name data vanished after recalculate BI</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="B12" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="B13" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <v>Under nominee, PA section basis pin code state and city details are not auto-fetched.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="B14" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <v>API wrapper App Number Duplicate Check</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="B15" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <v>API wrapper ANUR PIVC Link Generation</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="B16" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B17" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <v>API wrapper Filenet DMS</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B18" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <v>API wrapper Medical Scheduling / checkTPA</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="B19" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B20" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <v>API wrapper generate-bi</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B21" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <v>App Number Duplicate Check</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B22" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <v>Penny Drop Bank Validation</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="B23" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="B24" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <v>Unified Proposal API</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="B25" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <v>App Number Duplicate Check</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="B26" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <v>ANUR PIVC Link Generation</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="B27" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <v>Filenet DMS</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="B28" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="B29" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C29" s="1">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <v>Leave</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="B30" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="1" t="str">
+        <v>Leave</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="B31" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C31" s="1">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <v>Leave</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B32" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="str">
+        <v>Medical Scheduling / checkTPA</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="B33" s="1">
+        <v>158484</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <v>Daily Scrum Call</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+  </ignoredErrors>
 </worksheet>
 </file>